--- a/www/flightdata/xlsx/eoss-377.xlsx
+++ b/www/flightdata/xlsx/eoss-377.xlsx
@@ -3456,7 +3456,7 @@
         <v>19231.97</v>
       </c>
       <c r="I2">
-        <v>671</v>
+        <v>439</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
